--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\AR\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED24C553-4E01-4FF2-805D-03D92E1A5B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D53E092-2E66-41CA-BEEE-8CEBE277CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12735" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32925" yWindow="1350" windowWidth="23010" windowHeight="13800" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId20"/>
     <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId21"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="987">
   <si>
     <t>Source:</t>
   </si>
@@ -3012,9 +3012,6 @@
   </si>
   <si>
     <t>historical data.</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
   </si>
 </sst>
 </file>
@@ -3819,7 +3816,7 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3896,7 +3893,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -6411,9 +6407,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6451,9 +6447,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6486,26 +6482,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6538,26 +6517,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6731,24 +6693,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="56.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="B1" t="s">
-        <v>987</v>
-      </c>
-      <c r="C1" s="48">
-        <v>44907</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -6756,57 +6712,57 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>968</v>
       </c>
@@ -7679,127 +7635,127 @@
       </c>
       <c r="B4">
         <f>Data!H12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <f>Data!I12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <f>Data!J12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Data!K12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>Data!L12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <f>Data!M12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <f>Data!N12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <f>Data!O12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <f>Data!P12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f>Data!Q12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <f>Data!R12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <f>Data!S12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <f>Data!T12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <f>Data!U12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <f>Data!V12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <f>Data!W12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <f>Data!X12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <f>Data!Y12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <f>Data!Z12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4">
         <f>Data!AA12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V4">
         <f>Data!AB12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4">
         <f>Data!AC12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X4">
         <f>Data!AD12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <f>Data!AE12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z4">
         <f>Data!AF12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA4">
         <f>Data!AG12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB4">
         <f>Data!AH12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC4">
         <f>Data!AI12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD4">
         <f>Data!AJ12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE4">
         <f>Data!AK12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <f>Data!AL12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -10822,97 +10778,128 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <f>Data!H33</f>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <f>Data!I33</f>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <f>Data!J33</f>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <f>Data!K33</f>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <f>Data!L33</f>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <f>Data!M33</f>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <f>Data!N33</f>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <f>Data!O33</f>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <f>Data!P33</f>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <f>Data!Q33</f>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <f>Data!R33</f>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <f>Data!S33</f>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <f>Data!T33</f>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <f>Data!U33</f>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <f>Data!V33</f>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <f>Data!W33</f>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <f>Data!X33</f>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <f>Data!Y33</f>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <f>Data!Z33</f>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <f>Data!AA33</f>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <f>Data!AB33</f>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <f>Data!AC33</f>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <f>Data!AD33</f>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <f>Data!AE33</f>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>2</v>
+        <f>Data!AF33</f>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <f>Data!AG33</f>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <f>Data!AH33</f>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>2</v>
+        <f>Data!AI33</f>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <f>Data!AJ33</f>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <f>Data!AK33</f>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <f>Data!AL33</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -17727,7 +17714,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ76"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -25950,7 +25937,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AJ59"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -30524,7 +30511,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E495E93-490C-4630-BB04-9B57B46A213E}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -31679,7 +31666,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ262"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -55698,10 +55685,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
@@ -55911,16 +55898,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="8" width="23.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -58654,10 +58641,10 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="str">
         <f>IF(D12=E12,"n/a",IF(OR(C12="battery electric vehicle",C12="natural gas vehicle",C12="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -58665,127 +58652,127 @@
       </c>
       <c r="H12" s="22">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,I$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,J$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,K$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,L$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,M$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,N$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,O$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,P$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Q$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,R$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,S$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,T$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,U$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,V$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,W$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,X$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Y$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Z$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AA$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AB$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AC$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AD$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AE$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AF$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AG$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AH$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AI$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AJ$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AK$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AL$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AR\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D53E092-2E66-41CA-BEEE-8CEBE277CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F96561E-E86F-429B-8D6F-B6924C473A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32925" yWindow="1350" windowWidth="23010" windowHeight="13800" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="13035" windowHeight="16890" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="988">
   <si>
     <t>Source:</t>
   </si>
@@ -3012,6 +3012,9 @@
   </si>
   <si>
     <t>historical data.</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
   </si>
 </sst>
 </file>
@@ -3816,7 +3819,7 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3893,6 +3896,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -6693,18 +6697,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="56.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1" s="48">
+        <v>45258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -6712,57 +6722,57 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>968</v>
       </c>
@@ -7635,127 +7645,127 @@
       </c>
       <c r="B4">
         <f>Data!H12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <f>Data!I12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <f>Data!J12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <f>Data!K12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <f>Data!L12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <f>Data!M12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <f>Data!N12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <f>Data!O12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <f>Data!P12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <f>Data!Q12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <f>Data!R12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <f>Data!S12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <f>Data!T12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <f>Data!U12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4">
         <f>Data!V12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <f>Data!W12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <f>Data!X12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S4">
         <f>Data!Y12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4">
         <f>Data!Z12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4">
         <f>Data!AA12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V4">
         <f>Data!AB12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4">
         <f>Data!AC12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X4">
         <f>Data!AD12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4">
         <f>Data!AE12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z4">
         <f>Data!AF12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA4">
         <f>Data!AG12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB4">
         <f>Data!AH12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC4">
         <f>Data!AI12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD4">
         <f>Data!AJ12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE4">
         <f>Data!AK12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF4">
         <f>Data!AL12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -10778,128 +10788,97 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <f>Data!H33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C4">
-        <f>Data!I33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D4">
-        <f>Data!J33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E4">
-        <f>Data!K33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F4">
-        <f>Data!L33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G4">
-        <f>Data!M33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H4">
-        <f>Data!N33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I4">
-        <f>Data!O33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J4">
-        <f>Data!P33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K4">
-        <f>Data!Q33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="L4">
-        <f>Data!R33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="M4">
-        <f>Data!S33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="N4">
-        <f>Data!T33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O4">
-        <f>Data!U33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P4">
-        <f>Data!V33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q4">
-        <f>Data!W33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="R4">
-        <f>Data!X33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="S4">
-        <f>Data!Y33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="T4">
-        <f>Data!Z33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="U4">
-        <f>Data!AA33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="V4">
-        <f>Data!AB33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="W4">
-        <f>Data!AC33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="X4">
-        <f>Data!AD33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Y4">
-        <f>Data!AE33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Z4">
-        <f>Data!AF33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AA4">
-        <f>Data!AG33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AB4">
-        <f>Data!AH33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AC4">
-        <f>Data!AI33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AD4">
-        <f>Data!AJ33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AE4">
-        <f>Data!AK33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AF4">
-        <f>Data!AL33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -17714,7 +17693,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -25937,7 +25916,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AJ59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -30511,7 +30490,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E495E93-490C-4630-BB04-9B57B46A213E}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -31666,7 +31645,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ262"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -55685,10 +55664,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
@@ -55898,16 +55877,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="8" width="23.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -58641,10 +58620,10 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="7" t="str">
         <f>IF(D12=E12,"n/a",IF(OR(C12="battery electric vehicle",C12="natural gas vehicle",C12="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -58652,127 +58631,127 @@
       </c>
       <c r="H12" s="22">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,I$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,J$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,K$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,L$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,M$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,N$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,O$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,P$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Q$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,R$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,S$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,T$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,U$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,V$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,W$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,X$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Y$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Z$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AA$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AB$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AC$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AD$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AE$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AF$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AG$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AH$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AI$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AJ$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AK$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AL$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">
